--- a/data/test_data.xlsx
+++ b/data/test_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
   <si>
     <t>Setting</t>
   </si>
@@ -91,6 +91,12 @@
   </si>
   <si>
     <t>tests/fulfillment/test_online_sale_fulfillment.py</t>
+  </si>
+  <si>
+    <t>tests/fulfillment/test_uom_multi_unit_sale_fulfillment.py</t>
+  </si>
+  <si>
+    <t>2026-10-29</t>
   </si>
   <si>
     <t>ConfigName</t>
@@ -589,10 +595,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="1" width="30.428571428571427" customWidth="1"/>
+    <col min="2" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -628,13 +635,27 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
       <c r="D3" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -653,46 +674,46 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
